--- a/monsters.xlsx
+++ b/monsters.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>IMAGE</t>
   </si>
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Flip over another monster card after 4 turns.</t>
   </si>
   <si>
-    <t>16/24/40/64</t>
+    <t>5/8/12/16</t>
   </si>
   <si>
     <t xml:space="preserve">1 Gold</t>
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Takes 1 less damage from all sources.</t>
   </si>
   <si>
-    <t>10/20/32/56</t>
+    <t>5/7/10/12</t>
   </si>
   <si>
     <t xml:space="preserve">1 Ration</t>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">If you die fighting this monster, discard an equipment.</t>
   </si>
   <si>
-    <t>18/26/44/70</t>
+    <t>6/9/14/18</t>
   </si>
   <si>
     <t xml:space="preserve">2 Knowledge</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Player equipment is disabled in this combat.</t>
   </si>
   <si>
-    <t>12/20/30/45</t>
+    <t>5/7/11/14</t>
   </si>
   <si>
     <t>None</t>
@@ -168,9 +168,6 @@
     <t xml:space="preserve">Flip over another monster card immediately.</t>
   </si>
   <si>
-    <t>10/16/24/40</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 Gold</t>
   </si>
   <si>
@@ -192,7 +189,7 @@
     <t xml:space="preserve">Treasure Goblin</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw an equipment and place it facedown; the adventurer that deals the killing blow gets the item.</t>
+    <t xml:space="preserve">The adventurer that deals the killing blow gets the top item of the equipment deck for free.</t>
   </si>
 </sst>
 </file>
@@ -227,11 +224,12 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -947,7 +945,7 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -967,44 +965,44 @@
         <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="14.25">
       <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
         <v>52</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>53</v>
       </c>
-      <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
         <v>56</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>58</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
